--- a/similarities.xlsx
+++ b/similarities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\pep_wp4_eye_tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E4F7CD-A3E0-4857-9663-9FADD0327E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F71F5CE-B006-4D69-B972-90CFBA238F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="460">
   <si>
     <t xml:space="preserve">ObjectName </t>
   </si>
@@ -966,9 +966,6 @@
     <t>sculpture</t>
   </si>
   <si>
-    <t>semi-flush mount light</t>
-  </si>
-  <si>
     <t>shaker</t>
   </si>
   <si>
@@ -999,9 +996,6 @@
     <t>shower curtain</t>
   </si>
   <si>
-    <t>*shower door</t>
-  </si>
-  <si>
     <t>shower screen</t>
   </si>
   <si>
@@ -1402,6 +1396,15 @@
   </si>
   <si>
     <t>wine rack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">semi-flush </t>
+  </si>
+  <si>
+    <t>mount light</t>
+  </si>
+  <si>
+    <t>shower door</t>
   </si>
 </sst>
 </file>
@@ -1487,9 +1490,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1770,7 +1773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L306"/>
+  <dimension ref="A1:K306"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="17.88671875" customWidth="1"/>
@@ -1782,11 +1785,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
@@ -1797,7 +1795,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -1836,28 +1834,28 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>336</v>
+      <c r="B11" s="7" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1903,10 +1901,10 @@
         <v>22</v>
       </c>
       <c r="C18" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>385</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1942,7 +1940,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2042,7 +2040,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -2122,12 +2120,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>71</v>
       </c>
@@ -2138,12 +2136,12 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>78</v>
       </c>
@@ -2151,41 +2149,38 @@
         <v>79</v>
       </c>
       <c r="C52" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D52" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="4" t="s">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>83</v>
       </c>
-      <c r="F57">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>85</v>
       </c>
@@ -2193,12 +2188,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>88</v>
       </c>
@@ -2206,17 +2201,17 @@
         <v>89</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -2237,17 +2232,17 @@
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
+      <c r="A68" t="s">
         <v>96</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" t="s">
         <v>97</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" t="s">
         <v>98</v>
       </c>
-      <c r="D68" s="6" t="s">
-        <v>442</v>
+      <c r="D68" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -2281,6 +2276,9 @@
       <c r="C72" t="s">
         <v>136</v>
       </c>
+      <c r="D72" s="8" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -2344,7 +2342,7 @@
         <v>118</v>
       </c>
       <c r="C83" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D83" t="s">
         <v>279</v>
@@ -2355,10 +2353,10 @@
         <v>119</v>
       </c>
       <c r="B84" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C84" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2375,11 +2373,11 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
+      <c r="A87" t="s">
         <v>124</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2409,7 +2407,7 @@
         <v>132</v>
       </c>
       <c r="E90" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2479,11 +2477,11 @@
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="6" t="s">
+      <c r="A104" t="s">
         <v>147</v>
       </c>
       <c r="B104" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -2497,7 +2495,10 @@
         <v>312</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>353</v>
+      </c>
+      <c r="E105" s="8" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
@@ -2529,31 +2530,38 @@
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
+      <c r="A111" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B111" s="6"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="8"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="1" t="s">
+      <c r="A112" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="C112" s="1" t="s">
+      <c r="B112" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="C112" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D112" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="E112" s="1" t="s">
+      <c r="E112" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G112" s="1"/>
+      <c r="F112" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -2594,11 +2602,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="6"/>
-    </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="6" t="s">
+      <c r="A120" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2609,6 +2614,12 @@
       <c r="B121" t="s">
         <v>169</v>
       </c>
+      <c r="C121" t="s">
+        <v>261</v>
+      </c>
+      <c r="D121" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
@@ -2621,7 +2632,7 @@
         <v>308</v>
       </c>
       <c r="D122" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -2644,12 +2655,12 @@
       <c r="C125" t="s">
         <v>175</v>
       </c>
-      <c r="D125" s="6" t="s">
-        <v>447</v>
+      <c r="D125" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="6" t="s">
+      <c r="A126" t="s">
         <v>176</v>
       </c>
     </row>
@@ -2657,7 +2668,7 @@
       <c r="A127" t="s">
         <v>177</v>
       </c>
-      <c r="B127" s="7" t="s">
+      <c r="B127" s="6" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2666,12 +2677,12 @@
         <v>179</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>181</v>
       </c>
@@ -2679,28 +2690,28 @@
         <v>183</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="7" t="s">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="6" t="s">
         <v>187</v>
       </c>
       <c r="B135" t="s">
@@ -2710,17 +2721,17 @@
         <v>189</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="6" t="s">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>192</v>
       </c>
@@ -2728,38 +2739,44 @@
         <v>193</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>197</v>
       </c>
       <c r="B142" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" s="6" t="s">
+      <c r="C142" t="s">
+        <v>423</v>
+      </c>
+      <c r="D142" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
         <v>199</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B143" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>200</v>
       </c>
@@ -2767,52 +2784,40 @@
         <v>201</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="4" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>204</v>
       </c>
       <c r="B147" t="s">
         <v>209</v>
       </c>
-      <c r="C147" s="6" t="s">
+      <c r="C147" t="s">
         <v>221</v>
       </c>
       <c r="D147" t="s">
-        <v>345</v>
-      </c>
-      <c r="E147" t="s">
-        <v>350</v>
-      </c>
-      <c r="F147" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="G147" t="s">
-        <v>419</v>
-      </c>
-      <c r="H147" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="I147" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="K147" t="s">
-        <v>335</v>
-      </c>
-      <c r="L147" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>205</v>
       </c>
@@ -2823,12 +2828,12 @@
         <v>207</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>210</v>
       </c>
@@ -2836,17 +2841,17 @@
         <v>290</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>214</v>
       </c>
@@ -2854,15 +2859,15 @@
         <v>215</v>
       </c>
       <c r="C153" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>218</v>
       </c>
@@ -2870,17 +2875,17 @@
         <v>237</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="4" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>222</v>
       </c>
@@ -2888,12 +2893,12 @@
         <v>223</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>225</v>
       </c>
@@ -2925,7 +2930,7 @@
       <c r="A165" t="s">
         <v>231</v>
       </c>
-      <c r="B165" s="6" t="s">
+      <c r="B165" t="s">
         <v>258</v>
       </c>
     </row>
@@ -2946,23 +2951,23 @@
       <c r="B168" t="s">
         <v>249</v>
       </c>
-      <c r="C168" s="6" t="s">
+      <c r="C168" t="s">
         <v>250</v>
       </c>
-      <c r="D168" s="6" t="s">
+      <c r="D168" t="s">
         <v>251</v>
       </c>
       <c r="E168" t="s">
         <v>252</v>
       </c>
       <c r="F168" t="s">
+        <v>386</v>
+      </c>
+      <c r="G168" t="s">
+        <v>387</v>
+      </c>
+      <c r="H168" t="s">
         <v>388</v>
-      </c>
-      <c r="G168" t="s">
-        <v>389</v>
-      </c>
-      <c r="H168" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
@@ -2983,9 +2988,12 @@
         <v>239</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>240</v>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>348</v>
+      </c>
+      <c r="B173" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
@@ -2999,7 +3007,7 @@
         <v>246</v>
       </c>
       <c r="D174" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
@@ -3010,16 +3018,19 @@
         <v>245</v>
       </c>
     </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>109</v>
+      </c>
+      <c r="B176" t="s">
+        <v>438</v>
+      </c>
+    </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="6" t="s">
-        <v>253</v>
-      </c>
-    </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>255</v>
@@ -3028,7 +3039,13 @@
         <v>257</v>
       </c>
       <c r="C179" t="s">
-        <v>449</v>
+        <v>447</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E179" s="8" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
@@ -3044,11 +3061,6 @@
         <v>260</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="6" t="s">
-        <v>261</v>
-      </c>
-    </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>262</v>
@@ -3080,11 +3092,11 @@
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="4" t="s">
+      <c r="A188" s="8" t="s">
         <v>270</v>
       </c>
       <c r="B188" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.3">
@@ -3098,7 +3110,7 @@
         <v>274</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E189" t="s">
         <v>272</v>
@@ -3122,6 +3134,9 @@
       <c r="B194" t="s">
         <v>286</v>
       </c>
+      <c r="C194" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
@@ -3134,24 +3149,19 @@
         <v>285</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>284</v>
-      </c>
-    </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
+      <c r="A198" s="4" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
+      <c r="A199" s="4" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -3200,20 +3210,8 @@
         <v>302</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A211" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A212" s="4" t="s">
-        <v>306</v>
-      </c>
-    </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213" s="4" t="s">
-        <v>307</v>
-      </c>
+      <c r="A213" s="8"/>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
@@ -3230,168 +3228,163 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
+        <v>316</v>
+      </c>
+      <c r="B219" t="s">
         <v>317</v>
       </c>
-      <c r="B219" t="s">
-        <v>318</v>
-      </c>
       <c r="C219" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>324</v>
+        <v>459</v>
       </c>
       <c r="B224" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C224" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A225" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A226" s="4" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B231" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B236" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B238" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B239" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B241" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B245" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C245" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B246" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C246" t="s">
         <v>296</v>
@@ -3401,328 +3394,326 @@
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A247" s="6" t="s">
-        <v>362</v>
+      <c r="A247" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B251" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C251" t="s">
+        <v>325</v>
+      </c>
+      <c r="D251" t="s">
         <v>327</v>
-      </c>
-      <c r="D251" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B257" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B259" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B261" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B262" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C262" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B270" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B272" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C272" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B273" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C273" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B279" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B280" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B281" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B290" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A292" t="s">
-        <v>425</v>
+        <v>422</v>
+      </c>
+      <c r="B291" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B301" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
+        <v>432</v>
+      </c>
+      <c r="B302" t="s">
+        <v>433</v>
+      </c>
+      <c r="C302" t="s">
         <v>434</v>
       </c>
-      <c r="B302" t="s">
-        <v>435</v>
-      </c>
-      <c r="C302" t="s">
-        <v>436</v>
-      </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
-        <v>420</v>
+      <c r="A303" s="4" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>

--- a/similarities.xlsx
+++ b/similarities.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\pep_wp4_eye_tracking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F71F5CE-B006-4D69-B972-90CFBA238F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BDA93F-4CAA-4A80-AD0B-D23DC0133E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1005,9 +1005,6 @@
     <t>side table</t>
   </si>
   <si>
-    <t>*side</t>
-  </si>
-  <si>
     <t>side table crop</t>
   </si>
   <si>
@@ -1405,6 +1402,9 @@
   </si>
   <si>
     <t>shower door</t>
+  </si>
+  <si>
+    <t>side</t>
   </si>
 </sst>
 </file>
@@ -1442,12 +1442,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1466,7 +1460,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1483,16 +1483,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1773,7 +1774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K306"/>
+  <dimension ref="A1:K305"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="17.88671875" customWidth="1"/>
@@ -1795,7 +1796,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C4" t="s">
         <v>74</v>
@@ -1832,13 +1833,16 @@
       <c r="C8" t="s">
         <v>289</v>
       </c>
+      <c r="D8" s="6" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -1850,8 +1854,8 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>334</v>
+      <c r="B11" s="5" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -1900,25 +1904,19 @@
       <c r="B18" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>385</v>
+      <c r="C18" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="B19" t="s">
         <v>25</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -2019,7 +2017,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -2032,38 +2030,41 @@
       <c r="D33" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E33" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>59</v>
       </c>
@@ -2071,22 +2072,22 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>64</v>
       </c>
@@ -2100,23 +2101,23 @@
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="4" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2149,7 +2150,7 @@
         <v>79</v>
       </c>
       <c r="C52" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D52" t="s">
         <v>254</v>
@@ -2166,7 +2167,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="8" t="s">
+      <c r="A56" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2216,22 +2217,22 @@
         <v>92</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -2242,81 +2243,161 @@
         <v>98</v>
       </c>
       <c r="D68" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="6" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="6" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D72" s="6" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="E72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="6" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="6" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="6" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="6" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="4" t="s">
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="6" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
+      <c r="B79" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="6" t="s">
         <v>114</v>
       </c>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -2342,7 +2423,7 @@
         <v>118</v>
       </c>
       <c r="C83" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D83" t="s">
         <v>279</v>
@@ -2353,10 +2434,10 @@
         <v>119</v>
       </c>
       <c r="B84" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C84" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2376,8 +2457,8 @@
       <c r="A87" t="s">
         <v>124</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>455</v>
+      <c r="B87" s="4" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2407,7 +2488,7 @@
         <v>132</v>
       </c>
       <c r="E90" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2465,6 +2546,9 @@
       <c r="A101" t="s">
         <v>144</v>
       </c>
+      <c r="B101" s="9" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
@@ -2481,7 +2565,7 @@
         <v>147</v>
       </c>
       <c r="B104" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -2495,9 +2579,9 @@
         <v>312</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
-      </c>
-      <c r="E105" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="E105" t="s">
         <v>307</v>
       </c>
     </row>
@@ -2517,7 +2601,7 @@
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="1" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2530,37 +2614,31 @@
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="8" t="s">
+      <c r="A111" t="s">
         <v>156</v>
       </c>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="8"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="8" t="s">
+      <c r="A112" t="s">
         <v>157</v>
       </c>
-      <c r="B112" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="C112" s="8" t="s">
+      <c r="B112" t="s">
+        <v>443</v>
+      </c>
+      <c r="C112" t="s">
         <v>73</v>
       </c>
-      <c r="D112" s="8" t="s">
+      <c r="D112" t="s">
         <v>213</v>
       </c>
-      <c r="E112" s="8" t="s">
+      <c r="E112" t="s">
         <v>216</v>
       </c>
-      <c r="F112" s="8" t="s">
+      <c r="F112" t="s">
+        <v>456</v>
+      </c>
+      <c r="G112" t="s">
         <v>457</v>
-      </c>
-      <c r="G112" s="8" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -2632,7 +2710,7 @@
         <v>308</v>
       </c>
       <c r="D122" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
@@ -2656,7 +2734,7 @@
         <v>175</v>
       </c>
       <c r="D125" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
@@ -2668,9 +2746,6 @@
       <c r="A127" t="s">
         <v>177</v>
       </c>
-      <c r="B127" s="6" t="s">
-        <v>178</v>
-      </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
@@ -2678,7 +2753,7 @@
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="3" t="s">
+      <c r="A129" s="2" t="s">
         <v>180</v>
       </c>
     </row>
@@ -2711,9 +2786,6 @@
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="6" t="s">
-        <v>187</v>
-      </c>
       <c r="B135" t="s">
         <v>188</v>
       </c>
@@ -2762,7 +2834,7 @@
         <v>198</v>
       </c>
       <c r="C142" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D142" t="s">
         <v>240</v>
@@ -2785,9 +2857,7 @@
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A145" s="4" t="s">
-        <v>202</v>
-      </c>
+      <c r="A145" s="6"/>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
@@ -2805,16 +2875,19 @@
         <v>221</v>
       </c>
       <c r="D147" t="s">
-        <v>343</v>
+        <v>342</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>417</v>
       </c>
       <c r="G147" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I147" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K147" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.3">
@@ -2859,7 +2932,7 @@
         <v>215</v>
       </c>
       <c r="C153" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
@@ -2881,9 +2954,7 @@
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A157" s="4" t="s">
-        <v>220</v>
-      </c>
+      <c r="A157" s="6"/>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
@@ -2961,13 +3032,13 @@
         <v>252</v>
       </c>
       <c r="F168" t="s">
+        <v>385</v>
+      </c>
+      <c r="G168" t="s">
         <v>386</v>
       </c>
-      <c r="G168" t="s">
+      <c r="H168" t="s">
         <v>387</v>
-      </c>
-      <c r="H168" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
@@ -2990,10 +3061,10 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
+        <v>347</v>
+      </c>
+      <c r="B173" t="s">
         <v>348</v>
-      </c>
-      <c r="B173" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
@@ -3007,7 +3078,7 @@
         <v>246</v>
       </c>
       <c r="D174" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
@@ -3023,7 +3094,7 @@
         <v>109</v>
       </c>
       <c r="B176" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
@@ -3039,12 +3110,12 @@
         <v>257</v>
       </c>
       <c r="C179" t="s">
-        <v>447</v>
-      </c>
-      <c r="D179" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="D179" t="s">
         <v>305</v>
       </c>
-      <c r="E179" s="8" t="s">
+      <c r="E179" t="s">
         <v>306</v>
       </c>
     </row>
@@ -3092,7 +3163,7 @@
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A188" s="8" t="s">
+      <c r="A188" t="s">
         <v>270</v>
       </c>
       <c r="B188" t="s">
@@ -3110,7 +3181,7 @@
         <v>274</v>
       </c>
       <c r="D189" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E189" t="s">
         <v>272</v>
@@ -3150,18 +3221,18 @@
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="6" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" s="4" t="s">
+      <c r="A199" s="3" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -3210,9 +3281,6 @@
         <v>302</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213" s="8"/>
-    </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>309</v>
@@ -3269,122 +3337,120 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B224" t="s">
         <v>323</v>
       </c>
       <c r="C224" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A226" s="4" t="s">
-        <v>326</v>
-      </c>
+      <c r="A226" s="7"/>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A230" s="3" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A230" s="4" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
+        <v>330</v>
+      </c>
+      <c r="B231" t="s">
         <v>331</v>
-      </c>
-      <c r="B231" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B236" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
+        <v>340</v>
+      </c>
+      <c r="B238" t="s">
         <v>341</v>
-      </c>
-      <c r="B238" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B239" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
+      <c r="B241" t="s">
         <v>346</v>
       </c>
-      <c r="B241" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A244" s="4" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A244" s="8" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B245" t="s">
+        <v>355</v>
+      </c>
+      <c r="C245" t="s">
         <v>356</v>
       </c>
-      <c r="C245" t="s">
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
+      <c r="B246" t="s">
         <v>358</v>
-      </c>
-      <c r="B246" t="s">
-        <v>359</v>
       </c>
       <c r="C246" t="s">
         <v>296</v>
@@ -3392,328 +3458,324 @@
       <c r="D246" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E246" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
+        <v>363</v>
+      </c>
+      <c r="B251" t="s">
         <v>364</v>
-      </c>
-      <c r="B251" t="s">
-        <v>365</v>
       </c>
       <c r="C251" t="s">
         <v>325</v>
       </c>
       <c r="D251" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A253" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A255" s="4" t="s">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A255" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
         <v>369</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
+        <v>370</v>
+      </c>
+      <c r="B257" t="s">
         <v>371</v>
-      </c>
-      <c r="B257" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
+        <v>373</v>
+      </c>
+      <c r="B259" t="s">
         <v>374</v>
-      </c>
-      <c r="B259" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
+        <v>376</v>
+      </c>
+      <c r="B261" t="s">
         <v>377</v>
-      </c>
-      <c r="B261" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
+        <v>378</v>
+      </c>
+      <c r="B262" t="s">
         <v>379</v>
       </c>
-      <c r="B262" t="s">
-        <v>380</v>
-      </c>
       <c r="C262" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A268" s="4" t="s">
-        <v>454</v>
+        <v>383</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
+        <v>389</v>
+      </c>
+      <c r="B270" t="s">
         <v>390</v>
-      </c>
-      <c r="B270" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
+        <v>392</v>
+      </c>
+      <c r="B272" t="s">
         <v>393</v>
       </c>
-      <c r="B272" t="s">
-        <v>394</v>
-      </c>
       <c r="C272" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
+        <v>397</v>
+      </c>
+      <c r="B273" t="s">
         <v>398</v>
       </c>
-      <c r="B273" t="s">
-        <v>399</v>
-      </c>
       <c r="C273" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
+        <v>403</v>
+      </c>
+      <c r="B279" t="s">
         <v>404</v>
-      </c>
-      <c r="B279" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
+        <v>405</v>
+      </c>
+      <c r="B280" t="s">
         <v>406</v>
-      </c>
-      <c r="B280" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
+        <v>407</v>
+      </c>
+      <c r="B281" t="s">
         <v>408</v>
-      </c>
-      <c r="B281" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" s="3" t="s">
         <v>413</v>
-      </c>
-    </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A286" s="4" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
+        <v>419</v>
+      </c>
+      <c r="B290" t="s">
         <v>420</v>
-      </c>
-      <c r="B290" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B291" t="s">
         <v>1</v>
       </c>
+      <c r="C291" s="6" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A293" s="2" t="s">
-        <v>424</v>
+      <c r="A293" s="1" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B301" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
+        <v>431</v>
+      </c>
+      <c r="B302" t="s">
         <v>432</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C302" t="s">
         <v>433</v>
       </c>
-      <c r="C302" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A303" s="4" t="s">
-        <v>418</v>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
   </sheetData>
